--- a/templates/execution_table_template.xlsx
+++ b/templates/execution_table_template.xlsx
@@ -15,10 +15,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0;[Red]\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.00_);[Red]▲0.00_)"/>
+    <numFmt numFmtId="168" formatCode="#,##0_);[Red]▲#,##0"/>
+    <numFmt numFmtId="169" formatCode="0;[Red]▲0;-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -685,7 +688,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1102,6 +1105,120 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1427,7 +1544,7 @@
         </is>
       </c>
       <c r="N2" s="55" t="n"/>
-      <c r="O2" s="110" t="n"/>
+      <c r="O2" s="151" t="n"/>
       <c r="P2" s="55" t="n"/>
       <c r="Q2" s="9" t="n"/>
       <c r="R2" s="57" t="n"/>
@@ -1439,7 +1556,7 @@
           <t>株価</t>
         </is>
       </c>
-      <c r="B3" s="79" t="n"/>
+      <c r="B3" s="152" t="n"/>
       <c r="C3" s="57" t="inlineStr">
         <is>
           <t>円</t>
@@ -1498,49 +1615,49 @@
           <t>第1四半期</t>
         </is>
       </c>
-      <c r="C5" s="111" t="n"/>
-      <c r="D5" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E5" s="111" t="n"/>
-      <c r="F5" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G5" s="111" t="n"/>
-      <c r="H5" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I5" s="111" t="n"/>
-      <c r="J5" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K5" s="111" t="n"/>
-      <c r="L5" s="113" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M5" s="114" t="n"/>
-      <c r="N5" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O5" s="115" t="n"/>
-      <c r="P5" s="115" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q5" s="116" t="inlineStr">
+      <c r="C5" s="153" t="n"/>
+      <c r="D5" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E5" s="153" t="n"/>
+      <c r="F5" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G5" s="153" t="n"/>
+      <c r="H5" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I5" s="153" t="n"/>
+      <c r="J5" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K5" s="153" t="n"/>
+      <c r="L5" s="155" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M5" s="156" t="n"/>
+      <c r="N5" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O5" s="157" t="n"/>
+      <c r="P5" s="157" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q5" s="158" t="inlineStr">
         <is>
           <t>売上・経常利益：各決算短信の累計実績（億円）</t>
         </is>
@@ -1555,49 +1672,49 @@
           <t>第2四半期</t>
         </is>
       </c>
-      <c r="C6" s="117" t="n"/>
-      <c r="D6" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E6" s="117" t="n"/>
-      <c r="F6" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G6" s="117" t="n"/>
-      <c r="H6" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I6" s="117" t="n"/>
-      <c r="J6" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K6" s="117" t="n"/>
-      <c r="L6" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M6" s="119" t="n"/>
-      <c r="N6" s="120" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O6" s="121" t="n"/>
-      <c r="P6" s="122" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q6" s="123" t="inlineStr">
+      <c r="C6" s="159" t="n"/>
+      <c r="D6" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E6" s="159" t="n"/>
+      <c r="F6" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G6" s="159" t="n"/>
+      <c r="H6" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I6" s="159" t="n"/>
+      <c r="J6" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K6" s="159" t="n"/>
+      <c r="L6" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M6" s="161" t="n"/>
+      <c r="N6" s="162" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O6" s="163" t="n"/>
+      <c r="P6" s="164" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q6" s="165" t="inlineStr">
         <is>
           <t>株価：各四半期末の終値（円、休場日は直前営業日）</t>
         </is>
@@ -1612,49 +1729,49 @@
           <t>第3四半期</t>
         </is>
       </c>
-      <c r="C7" s="117" t="n"/>
-      <c r="D7" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E7" s="117" t="n"/>
-      <c r="F7" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G7" s="117" t="n"/>
-      <c r="H7" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I7" s="117" t="n"/>
-      <c r="J7" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K7" s="117" t="n"/>
-      <c r="L7" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M7" s="119" t="n"/>
-      <c r="N7" s="125" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O7" s="117" t="n"/>
-      <c r="P7" s="122" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q7" s="122" t="inlineStr">
+      <c r="C7" s="159" t="n"/>
+      <c r="D7" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E7" s="159" t="n"/>
+      <c r="F7" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G7" s="159" t="n"/>
+      <c r="H7" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I7" s="159" t="n"/>
+      <c r="J7" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K7" s="159" t="n"/>
+      <c r="L7" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M7" s="161" t="n"/>
+      <c r="N7" s="167" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O7" s="159" t="n"/>
+      <c r="P7" s="164" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q7" s="164" t="inlineStr">
         <is>
           <t>予想年度は会社の通期予想のみ、四半期は未発表</t>
         </is>
@@ -1669,49 +1786,49 @@
           <t>決算</t>
         </is>
       </c>
-      <c r="C8" s="126" t="n"/>
-      <c r="D8" s="127" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E8" s="126" t="n"/>
-      <c r="F8" s="127" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G8" s="126" t="n"/>
-      <c r="H8" s="127" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I8" s="126" t="n"/>
-      <c r="J8" s="127" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K8" s="126" t="n"/>
-      <c r="L8" s="127" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M8" s="128" t="n"/>
-      <c r="N8" s="129" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O8" s="130" t="n"/>
-      <c r="P8" s="123" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q8" s="131" t="inlineStr">
+      <c r="C8" s="168" t="n"/>
+      <c r="D8" s="169" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E8" s="168" t="n"/>
+      <c r="F8" s="169" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G8" s="168" t="n"/>
+      <c r="H8" s="169" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I8" s="168" t="n"/>
+      <c r="J8" s="169" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K8" s="168" t="n"/>
+      <c r="L8" s="169" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M8" s="170" t="n"/>
+      <c r="N8" s="171" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O8" s="172" t="n"/>
+      <c r="P8" s="165" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q8" s="173" t="inlineStr">
         <is>
           <t>業績出典：J-Quants /fins/summary</t>
         </is>
@@ -1730,49 +1847,49 @@
           <t>第1四半期</t>
         </is>
       </c>
-      <c r="C9" s="132" t="n"/>
-      <c r="D9" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E9" s="133" t="n"/>
-      <c r="F9" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G9" s="133" t="n"/>
-      <c r="H9" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I9" s="133" t="n"/>
-      <c r="J9" s="112" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K9" s="133" t="n"/>
-      <c r="L9" s="113" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M9" s="134" t="n"/>
-      <c r="N9" s="120" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O9" s="115" t="n"/>
-      <c r="P9" s="135" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q9" s="123" t="inlineStr">
+      <c r="C9" s="174" t="n"/>
+      <c r="D9" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E9" s="175" t="n"/>
+      <c r="F9" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G9" s="175" t="n"/>
+      <c r="H9" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I9" s="175" t="n"/>
+      <c r="J9" s="154" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K9" s="175" t="n"/>
+      <c r="L9" s="155" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M9" s="176" t="n"/>
+      <c r="N9" s="162" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O9" s="157" t="n"/>
+      <c r="P9" s="177" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q9" s="165" t="inlineStr">
         <is>
           <t>株価出典：J-Quants /equities/bars/daily</t>
         </is>
@@ -1787,49 +1904,49 @@
           <t>第2四半期</t>
         </is>
       </c>
-      <c r="C10" s="136" t="n"/>
-      <c r="D10" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E10" s="136" t="n"/>
-      <c r="F10" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G10" s="136" t="n"/>
-      <c r="H10" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I10" s="136" t="n"/>
-      <c r="J10" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K10" s="136" t="n"/>
-      <c r="L10" s="118" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M10" s="137" t="n"/>
-      <c r="N10" s="120" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O10" s="121" t="n"/>
-      <c r="P10" s="122" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q10" s="122" t="n"/>
+      <c r="C10" s="178" t="n"/>
+      <c r="D10" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E10" s="178" t="n"/>
+      <c r="F10" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G10" s="178" t="n"/>
+      <c r="H10" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I10" s="178" t="n"/>
+      <c r="J10" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K10" s="178" t="n"/>
+      <c r="L10" s="160" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M10" s="179" t="n"/>
+      <c r="N10" s="162" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O10" s="163" t="n"/>
+      <c r="P10" s="164" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q10" s="164" t="n"/>
       <c r="R10" s="57" t="n"/>
       <c r="S10" s="57" t="n"/>
     </row>
@@ -1840,49 +1957,49 @@
           <t>第3四半期</t>
         </is>
       </c>
-      <c r="C11" s="136" t="n"/>
-      <c r="D11" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E11" s="136" t="n"/>
-      <c r="F11" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G11" s="136" t="n"/>
-      <c r="H11" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I11" s="136" t="n"/>
-      <c r="J11" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K11" s="136" t="n"/>
-      <c r="L11" s="124" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M11" s="137" t="n"/>
-      <c r="N11" s="125" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O11" s="121" t="n"/>
-      <c r="P11" s="122" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q11" s="122" t="n"/>
+      <c r="C11" s="178" t="n"/>
+      <c r="D11" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E11" s="178" t="n"/>
+      <c r="F11" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G11" s="178" t="n"/>
+      <c r="H11" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I11" s="178" t="n"/>
+      <c r="J11" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K11" s="178" t="n"/>
+      <c r="L11" s="166" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M11" s="179" t="n"/>
+      <c r="N11" s="167" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O11" s="163" t="n"/>
+      <c r="P11" s="164" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q11" s="164" t="n"/>
       <c r="R11" s="57" t="n"/>
       <c r="S11" s="57" t="n"/>
     </row>
@@ -1893,49 +2010,49 @@
           <t>決算</t>
         </is>
       </c>
-      <c r="C12" s="136" t="n"/>
-      <c r="D12" s="121" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="E12" s="136" t="n"/>
-      <c r="F12" s="121" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="G12" s="117" t="n"/>
-      <c r="H12" s="121" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="I12" s="117" t="n"/>
-      <c r="J12" s="121" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="K12" s="117" t="n"/>
-      <c r="L12" s="121" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="M12" s="119" t="n"/>
-      <c r="N12" s="125" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="O12" s="117" t="n"/>
-      <c r="P12" s="122" t="inlineStr">
-        <is>
-          <t>億</t>
-        </is>
-      </c>
-      <c r="Q12" s="122" t="n"/>
+      <c r="C12" s="178" t="n"/>
+      <c r="D12" s="163" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="E12" s="178" t="n"/>
+      <c r="F12" s="163" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="G12" s="159" t="n"/>
+      <c r="H12" s="163" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="I12" s="159" t="n"/>
+      <c r="J12" s="163" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="K12" s="159" t="n"/>
+      <c r="L12" s="163" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="M12" s="161" t="n"/>
+      <c r="N12" s="167" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="O12" s="159" t="n"/>
+      <c r="P12" s="164" t="inlineStr">
+        <is>
+          <t>億</t>
+        </is>
+      </c>
+      <c r="Q12" s="164" t="n"/>
       <c r="R12" s="57" t="n"/>
       <c r="S12" s="57" t="n"/>
     </row>
@@ -1996,43 +2113,43 @@
           <t>第1四半期</t>
         </is>
       </c>
-      <c r="C14" s="111" t="n"/>
-      <c r="D14" s="112" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="E14" s="111" t="n"/>
-      <c r="F14" s="112" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="n"/>
-      <c r="H14" s="112" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="I14" s="111" t="n"/>
-      <c r="J14" s="112" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="K14" s="111" t="n"/>
-      <c r="L14" s="113" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="M14" s="114" t="n"/>
-      <c r="N14" s="112" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="O14" s="138" t="n"/>
+      <c r="C14" s="153" t="n"/>
+      <c r="D14" s="154" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E14" s="153" t="n"/>
+      <c r="F14" s="154" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="G14" s="153" t="n"/>
+      <c r="H14" s="154" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="I14" s="153" t="n"/>
+      <c r="J14" s="154" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="K14" s="153" t="n"/>
+      <c r="L14" s="155" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="M14" s="156" t="n"/>
+      <c r="N14" s="154" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="O14" s="180" t="n"/>
       <c r="P14" s="15" t="inlineStr">
         <is>
           <t>円</t>
@@ -2049,43 +2166,43 @@
           <t>第2四半期</t>
         </is>
       </c>
-      <c r="C15" s="117" t="n"/>
-      <c r="D15" s="118" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="E15" s="117" t="n"/>
-      <c r="F15" s="118" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="G15" s="139" t="n"/>
-      <c r="H15" s="118" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="I15" s="139" t="n"/>
-      <c r="J15" s="118" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="K15" s="117" t="n"/>
-      <c r="L15" s="118" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="M15" s="119" t="n"/>
-      <c r="N15" s="120" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="O15" s="121" t="n"/>
+      <c r="C15" s="159" t="n"/>
+      <c r="D15" s="160" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E15" s="159" t="n"/>
+      <c r="F15" s="160" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="G15" s="181" t="n"/>
+      <c r="H15" s="160" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="I15" s="181" t="n"/>
+      <c r="J15" s="160" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="K15" s="159" t="n"/>
+      <c r="L15" s="160" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="M15" s="161" t="n"/>
+      <c r="N15" s="162" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="O15" s="163" t="n"/>
       <c r="P15" s="16" t="inlineStr">
         <is>
           <t>円</t>
@@ -2102,43 +2219,43 @@
           <t>第3四半期</t>
         </is>
       </c>
-      <c r="C16" s="117" t="n"/>
-      <c r="D16" s="124" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="E16" s="117" t="n"/>
-      <c r="F16" s="124" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="G16" s="117" t="n"/>
-      <c r="H16" s="124" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="I16" s="117" t="n"/>
-      <c r="J16" s="124" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="K16" s="117" t="n"/>
-      <c r="L16" s="124" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="M16" s="119" t="n"/>
-      <c r="N16" s="125" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="O16" s="121" t="n"/>
+      <c r="C16" s="159" t="n"/>
+      <c r="D16" s="166" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E16" s="159" t="n"/>
+      <c r="F16" s="166" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="G16" s="159" t="n"/>
+      <c r="H16" s="166" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="I16" s="159" t="n"/>
+      <c r="J16" s="166" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="K16" s="159" t="n"/>
+      <c r="L16" s="166" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="M16" s="161" t="n"/>
+      <c r="N16" s="167" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="O16" s="163" t="n"/>
       <c r="P16" s="16" t="inlineStr">
         <is>
           <t>円</t>
@@ -2155,43 +2272,43 @@
           <t>決算</t>
         </is>
       </c>
-      <c r="C17" s="140" t="n"/>
-      <c r="D17" s="127" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="E17" s="140" t="n"/>
-      <c r="F17" s="127" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="G17" s="140" t="n"/>
-      <c r="H17" s="127" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="I17" s="140" t="n"/>
-      <c r="J17" s="127" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="K17" s="140" t="n"/>
-      <c r="L17" s="127" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="M17" s="141" t="n"/>
-      <c r="N17" s="129" t="inlineStr">
-        <is>
-          <t>円</t>
-        </is>
-      </c>
-      <c r="O17" s="142" t="n"/>
+      <c r="C17" s="182" t="n"/>
+      <c r="D17" s="169" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="E17" s="182" t="n"/>
+      <c r="F17" s="169" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="G17" s="182" t="n"/>
+      <c r="H17" s="169" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="I17" s="182" t="n"/>
+      <c r="J17" s="169" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="K17" s="182" t="n"/>
+      <c r="L17" s="169" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="M17" s="183" t="n"/>
+      <c r="N17" s="171" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="O17" s="184" t="n"/>
       <c r="P17" s="17" t="inlineStr">
         <is>
           <t>円</t>
@@ -2416,7 +2533,7 @@
         <v/>
       </c>
       <c r="N26" s="145" t="n"/>
-      <c r="O26" s="26" t="n"/>
+      <c r="O26" s="185" t="n"/>
       <c r="P26" s="27" t="n"/>
       <c r="Q26" s="28" t="n"/>
     </row>
@@ -2457,7 +2574,7 @@
         <v/>
       </c>
       <c r="N27" s="146" t="n"/>
-      <c r="O27" s="40" t="n"/>
+      <c r="O27" s="186" t="n"/>
       <c r="P27" s="55" t="n"/>
       <c r="Q27" s="41" t="n"/>
     </row>
@@ -2498,7 +2615,7 @@
         <v/>
       </c>
       <c r="N28" s="147" t="n"/>
-      <c r="O28" s="40" t="n"/>
+      <c r="O28" s="186" t="n"/>
       <c r="P28" s="55" t="n"/>
       <c r="Q28" s="41" t="n"/>
     </row>
@@ -2539,7 +2656,7 @@
         <v/>
       </c>
       <c r="N29" s="148" t="n"/>
-      <c r="O29" s="23" t="n"/>
+      <c r="O29" s="187" t="n"/>
       <c r="P29" s="24" t="n"/>
       <c r="Q29" s="25" t="n"/>
     </row>
@@ -2558,9 +2675,9 @@
       <c r="L30" s="149" t="n"/>
       <c r="M30" s="149" t="n"/>
       <c r="N30" s="149" t="n"/>
-      <c r="O30" s="108" t="n"/>
-      <c r="P30" s="108" t="n"/>
-      <c r="Q30" s="108" t="n"/>
+      <c r="O30" s="188" t="n"/>
+      <c r="P30" s="188" t="n"/>
+      <c r="Q30" s="188" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1" s="109">
       <c r="A31" s="57" t="n"/>

--- a/templates/execution_table_template.xlsx
+++ b/templates/execution_table_template.xlsx
@@ -15,13 +15,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0;[Red]\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00_);[Red]▲0.00_)"/>
     <numFmt numFmtId="168" formatCode="#,##0_);[Red]▲#,##0"/>
     <numFmt numFmtId="169" formatCode="0;[Red]▲0;-"/>
+    <numFmt numFmtId="170" formatCode="0.0_);[Red]▲0.0_)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -688,7 +689,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1219,6 +1220,15 @@
     </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1544,7 +1554,7 @@
         </is>
       </c>
       <c r="N2" s="55" t="n"/>
-      <c r="O2" s="151" t="n"/>
+      <c r="O2" s="191" t="n"/>
       <c r="P2" s="55" t="n"/>
       <c r="Q2" s="9" t="n"/>
       <c r="R2" s="57" t="n"/>
@@ -2063,37 +2073,37 @@
           <t>利益率</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="189">
         <f>IFERROR(C12/C8,"")</f>
         <v/>
       </c>
       <c r="D13" s="66" t="n"/>
-      <c r="E13" s="21">
+      <c r="E13" s="189">
         <f>IFERROR(E12/E8,"")</f>
         <v/>
       </c>
       <c r="F13" s="66" t="n"/>
-      <c r="G13" s="21">
+      <c r="G13" s="189">
         <f>IFERROR(G12/G8,"")</f>
         <v/>
       </c>
       <c r="H13" s="66" t="n"/>
-      <c r="I13" s="21">
+      <c r="I13" s="189">
         <f>IFERROR(I12/I8,"")</f>
         <v/>
       </c>
       <c r="J13" s="66" t="n"/>
-      <c r="K13" s="21">
+      <c r="K13" s="189">
         <f>IFERROR(K12/K8,"")</f>
         <v/>
       </c>
       <c r="L13" s="66" t="n"/>
-      <c r="M13" s="60">
+      <c r="M13" s="190">
         <f>IFERROR(M12/M8,"")</f>
         <v/>
       </c>
       <c r="N13" s="22" t="n"/>
-      <c r="O13" s="21">
+      <c r="O13" s="189">
         <f>IFERROR(O12/O8,"")</f>
         <v/>
       </c>

--- a/templates/execution_table_template.xlsx
+++ b/templates/execution_table_template.xlsx
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0;[Red]\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -23,6 +23,7 @@
     <numFmt numFmtId="168" formatCode="#,##0_);[Red]▲#,##0"/>
     <numFmt numFmtId="169" formatCode="0;[Red]▲0;-"/>
     <numFmt numFmtId="170" formatCode="0.0_);[Red]▲0.0_)"/>
+    <numFmt numFmtId="171" formatCode="0.00;[Red]▲0.00;-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -689,7 +690,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1229,6 +1230,33 @@
     </xf>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1857,43 +1885,43 @@
           <t>第1四半期</t>
         </is>
       </c>
-      <c r="C9" s="174" t="n"/>
+      <c r="C9" s="192" t="n"/>
       <c r="D9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E9" s="175" t="n"/>
+      <c r="E9" s="193" t="n"/>
       <c r="F9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G9" s="175" t="n"/>
+      <c r="G9" s="193" t="n"/>
       <c r="H9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I9" s="175" t="n"/>
+      <c r="I9" s="193" t="n"/>
       <c r="J9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K9" s="175" t="n"/>
+      <c r="K9" s="193" t="n"/>
       <c r="L9" s="155" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M9" s="176" t="n"/>
+      <c r="M9" s="194" t="n"/>
       <c r="N9" s="162" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O9" s="157" t="n"/>
+      <c r="O9" s="195" t="n"/>
       <c r="P9" s="177" t="inlineStr">
         <is>
           <t>億</t>
@@ -1914,43 +1942,43 @@
           <t>第2四半期</t>
         </is>
       </c>
-      <c r="C10" s="178" t="n"/>
+      <c r="C10" s="196" t="n"/>
       <c r="D10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E10" s="178" t="n"/>
+      <c r="E10" s="196" t="n"/>
       <c r="F10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G10" s="178" t="n"/>
+      <c r="G10" s="196" t="n"/>
       <c r="H10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I10" s="178" t="n"/>
+      <c r="I10" s="196" t="n"/>
       <c r="J10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K10" s="178" t="n"/>
+      <c r="K10" s="196" t="n"/>
       <c r="L10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M10" s="179" t="n"/>
+      <c r="M10" s="197" t="n"/>
       <c r="N10" s="162" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O10" s="163" t="n"/>
+      <c r="O10" s="198" t="n"/>
       <c r="P10" s="164" t="inlineStr">
         <is>
           <t>億</t>
@@ -1967,43 +1995,43 @@
           <t>第3四半期</t>
         </is>
       </c>
-      <c r="C11" s="178" t="n"/>
+      <c r="C11" s="196" t="n"/>
       <c r="D11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E11" s="178" t="n"/>
+      <c r="E11" s="196" t="n"/>
       <c r="F11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G11" s="178" t="n"/>
+      <c r="G11" s="196" t="n"/>
       <c r="H11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I11" s="178" t="n"/>
+      <c r="I11" s="196" t="n"/>
       <c r="J11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K11" s="178" t="n"/>
+      <c r="K11" s="196" t="n"/>
       <c r="L11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M11" s="179" t="n"/>
+      <c r="M11" s="197" t="n"/>
       <c r="N11" s="167" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O11" s="163" t="n"/>
+      <c r="O11" s="198" t="n"/>
       <c r="P11" s="164" t="inlineStr">
         <is>
           <t>億</t>
@@ -2020,43 +2048,43 @@
           <t>決算</t>
         </is>
       </c>
-      <c r="C12" s="178" t="n"/>
+      <c r="C12" s="196" t="n"/>
       <c r="D12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E12" s="178" t="n"/>
+      <c r="E12" s="196" t="n"/>
       <c r="F12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G12" s="159" t="n"/>
+      <c r="G12" s="199" t="n"/>
       <c r="H12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I12" s="159" t="n"/>
+      <c r="I12" s="199" t="n"/>
       <c r="J12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K12" s="159" t="n"/>
+      <c r="K12" s="199" t="n"/>
       <c r="L12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M12" s="161" t="n"/>
+      <c r="M12" s="200" t="n"/>
       <c r="N12" s="167" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O12" s="159" t="n"/>
+      <c r="O12" s="199" t="n"/>
       <c r="P12" s="164" t="inlineStr">
         <is>
           <t>億</t>
@@ -2074,37 +2102,37 @@
         </is>
       </c>
       <c r="C13" s="189">
-        <f>IFERROR(C12/C8,"")</f>
+        <f>IFERROR(TRUNC(C12/C8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="D13" s="66" t="n"/>
       <c r="E13" s="189">
-        <f>IFERROR(E12/E8,"")</f>
+        <f>IFERROR(TRUNC(E12/E8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="66" t="n"/>
       <c r="G13" s="189">
-        <f>IFERROR(G12/G8,"")</f>
+        <f>IFERROR(TRUNC(G12/G8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="H13" s="66" t="n"/>
       <c r="I13" s="189">
-        <f>IFERROR(I12/I8,"")</f>
+        <f>IFERROR(TRUNC(I12/I8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="J13" s="66" t="n"/>
       <c r="K13" s="189">
-        <f>IFERROR(K12/K8,"")</f>
+        <f>IFERROR(TRUNC(K12/K8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="L13" s="66" t="n"/>
       <c r="M13" s="190">
-        <f>IFERROR(M12/M8,"")</f>
+        <f>IFERROR(TRUNC(M12/M8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="189">
-        <f>IFERROR(O12/O8,"")</f>
+        <f>IFERROR(TRUNC(O12/O8*1000)/1000,"")</f>
         <v/>
       </c>
       <c r="P13" s="14" t="n"/>
@@ -2514,32 +2542,32 @@
         </is>
       </c>
       <c r="C26" s="144">
-        <f>SUM(C9/C5)</f>
+        <f>TRUNC((C9/C5)*1000)/1000</f>
         <v/>
       </c>
       <c r="D26" s="145" t="n"/>
       <c r="E26" s="144">
-        <f>SUM(E9/E5)</f>
+        <f>TRUNC((E9/E5)*1000)/1000</f>
         <v/>
       </c>
       <c r="F26" s="145" t="n"/>
       <c r="G26" s="144">
-        <f>SUM(G9/G5)</f>
+        <f>TRUNC((G9/G5)*1000)/1000</f>
         <v/>
       </c>
       <c r="H26" s="145" t="n"/>
       <c r="I26" s="144">
-        <f>SUM(I9/I5)</f>
+        <f>TRUNC((I9/I5)*1000)/1000</f>
         <v/>
       </c>
       <c r="J26" s="145" t="n"/>
       <c r="K26" s="144">
-        <f>SUM(K9/K5)</f>
+        <f>TRUNC((K9/K5)*1000)/1000</f>
         <v/>
       </c>
       <c r="L26" s="145" t="n"/>
       <c r="M26" s="144">
-        <f>SUM(M9/M5)</f>
+        <f>TRUNC((M9/M5)*1000)/1000</f>
         <v/>
       </c>
       <c r="N26" s="145" t="n"/>
@@ -2555,32 +2583,32 @@
         </is>
       </c>
       <c r="C27" s="144">
-        <f>SUM(C10/C6)</f>
+        <f>TRUNC((C10/C6)*1000)/1000</f>
         <v/>
       </c>
       <c r="D27" s="146" t="n"/>
       <c r="E27" s="144">
-        <f>SUM(E10/E6)</f>
+        <f>TRUNC((E10/E6)*1000)/1000</f>
         <v/>
       </c>
       <c r="F27" s="146" t="n"/>
       <c r="G27" s="144">
-        <f>SUM(G10/G6)</f>
+        <f>TRUNC((G10/G6)*1000)/1000</f>
         <v/>
       </c>
       <c r="H27" s="146" t="n"/>
       <c r="I27" s="144">
-        <f>SUM(I10/I6)</f>
+        <f>TRUNC((I10/I6)*1000)/1000</f>
         <v/>
       </c>
       <c r="J27" s="146" t="n"/>
       <c r="K27" s="144">
-        <f>SUM(K10/K6)</f>
+        <f>TRUNC((K10/K6)*1000)/1000</f>
         <v/>
       </c>
       <c r="L27" s="146" t="n"/>
       <c r="M27" s="144">
-        <f>SUM(M10/M6)</f>
+        <f>TRUNC((M10/M6)*1000)/1000</f>
         <v/>
       </c>
       <c r="N27" s="146" t="n"/>
@@ -2596,32 +2624,32 @@
         </is>
       </c>
       <c r="C28" s="144">
-        <f>SUM(C11/C7)</f>
+        <f>TRUNC((C11/C7)*1000)/1000</f>
         <v/>
       </c>
       <c r="D28" s="147" t="n"/>
       <c r="E28" s="144">
-        <f>SUM(E11/E7)</f>
+        <f>TRUNC((E11/E7)*1000)/1000</f>
         <v/>
       </c>
       <c r="F28" s="147" t="n"/>
       <c r="G28" s="144">
-        <f>SUM(G11/G7)</f>
+        <f>TRUNC((G11/G7)*1000)/1000</f>
         <v/>
       </c>
       <c r="H28" s="147" t="n"/>
       <c r="I28" s="144">
-        <f>SUM(I11/I7)</f>
+        <f>TRUNC((I11/I7)*1000)/1000</f>
         <v/>
       </c>
       <c r="J28" s="147" t="n"/>
       <c r="K28" s="144">
-        <f>SUM(K11/K7)</f>
+        <f>TRUNC((K11/K7)*1000)/1000</f>
         <v/>
       </c>
       <c r="L28" s="147" t="n"/>
       <c r="M28" s="144">
-        <f>SUM(M11/M7)</f>
+        <f>TRUNC((M11/M7)*1000)/1000</f>
         <v/>
       </c>
       <c r="N28" s="147" t="n"/>
@@ -2637,32 +2665,32 @@
         </is>
       </c>
       <c r="C29" s="144">
-        <f>SUM(C12/C8)</f>
+        <f>TRUNC((C12/C8)*1000)/1000</f>
         <v/>
       </c>
       <c r="D29" s="148" t="n"/>
       <c r="E29" s="144">
-        <f>SUM(E12/E8)</f>
+        <f>TRUNC((E12/E8)*1000)/1000</f>
         <v/>
       </c>
       <c r="F29" s="148" t="n"/>
       <c r="G29" s="144">
-        <f>SUM(G12/G8)</f>
+        <f>TRUNC((G12/G8)*1000)/1000</f>
         <v/>
       </c>
       <c r="H29" s="148" t="n"/>
       <c r="I29" s="144">
-        <f>SUM(I12/I8)</f>
+        <f>TRUNC((I12/I8)*1000)/1000</f>
         <v/>
       </c>
       <c r="J29" s="148" t="n"/>
       <c r="K29" s="144">
-        <f>SUM(K12/K8)</f>
+        <f>TRUNC((K12/K8)*1000)/1000</f>
         <v/>
       </c>
       <c r="L29" s="148" t="n"/>
       <c r="M29" s="144">
-        <f>SUM(M12/M8)</f>
+        <f>TRUNC((M12/M8)*1000)/1000</f>
         <v/>
       </c>
       <c r="N29" s="148" t="n"/>

--- a/templates/execution_table_template.xlsx
+++ b/templates/execution_table_template.xlsx
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0;[Red]\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -24,6 +24,7 @@
     <numFmt numFmtId="169" formatCode="0;[Red]▲0;-"/>
     <numFmt numFmtId="170" formatCode="0.0_);[Red]▲0.0_)"/>
     <numFmt numFmtId="171" formatCode="0.00;[Red]▲0.00;-"/>
+    <numFmt numFmtId="172" formatCode="0.0;[Red]▲0.0;-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -690,7 +691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1256,6 +1257,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1885,43 +1913,43 @@
           <t>第1四半期</t>
         </is>
       </c>
-      <c r="C9" s="192" t="n"/>
+      <c r="C9" s="201" t="n"/>
       <c r="D9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E9" s="193" t="n"/>
+      <c r="E9" s="202" t="n"/>
       <c r="F9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G9" s="193" t="n"/>
+      <c r="G9" s="202" t="n"/>
       <c r="H9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I9" s="193" t="n"/>
+      <c r="I9" s="202" t="n"/>
       <c r="J9" s="154" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K9" s="193" t="n"/>
+      <c r="K9" s="202" t="n"/>
       <c r="L9" s="155" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M9" s="194" t="n"/>
+      <c r="M9" s="203" t="n"/>
       <c r="N9" s="162" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O9" s="195" t="n"/>
+      <c r="O9" s="204" t="n"/>
       <c r="P9" s="177" t="inlineStr">
         <is>
           <t>億</t>
@@ -1942,43 +1970,43 @@
           <t>第2四半期</t>
         </is>
       </c>
-      <c r="C10" s="196" t="n"/>
+      <c r="C10" s="205" t="n"/>
       <c r="D10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E10" s="196" t="n"/>
+      <c r="E10" s="205" t="n"/>
       <c r="F10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G10" s="196" t="n"/>
+      <c r="G10" s="205" t="n"/>
       <c r="H10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I10" s="196" t="n"/>
+      <c r="I10" s="205" t="n"/>
       <c r="J10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K10" s="196" t="n"/>
+      <c r="K10" s="205" t="n"/>
       <c r="L10" s="160" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M10" s="197" t="n"/>
+      <c r="M10" s="206" t="n"/>
       <c r="N10" s="162" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O10" s="198" t="n"/>
+      <c r="O10" s="207" t="n"/>
       <c r="P10" s="164" t="inlineStr">
         <is>
           <t>億</t>
@@ -1995,43 +2023,43 @@
           <t>第3四半期</t>
         </is>
       </c>
-      <c r="C11" s="196" t="n"/>
+      <c r="C11" s="205" t="n"/>
       <c r="D11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E11" s="196" t="n"/>
+      <c r="E11" s="205" t="n"/>
       <c r="F11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G11" s="196" t="n"/>
+      <c r="G11" s="205" t="n"/>
       <c r="H11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I11" s="196" t="n"/>
+      <c r="I11" s="205" t="n"/>
       <c r="J11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K11" s="196" t="n"/>
+      <c r="K11" s="205" t="n"/>
       <c r="L11" s="166" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M11" s="197" t="n"/>
+      <c r="M11" s="206" t="n"/>
       <c r="N11" s="167" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O11" s="198" t="n"/>
+      <c r="O11" s="207" t="n"/>
       <c r="P11" s="164" t="inlineStr">
         <is>
           <t>億</t>
@@ -2048,43 +2076,43 @@
           <t>決算</t>
         </is>
       </c>
-      <c r="C12" s="196" t="n"/>
+      <c r="C12" s="205" t="n"/>
       <c r="D12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="E12" s="196" t="n"/>
+      <c r="E12" s="205" t="n"/>
       <c r="F12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="G12" s="199" t="n"/>
+      <c r="G12" s="208" t="n"/>
       <c r="H12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="I12" s="199" t="n"/>
+      <c r="I12" s="208" t="n"/>
       <c r="J12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="K12" s="199" t="n"/>
+      <c r="K12" s="208" t="n"/>
       <c r="L12" s="163" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="M12" s="200" t="n"/>
+      <c r="M12" s="209" t="n"/>
       <c r="N12" s="167" t="inlineStr">
         <is>
           <t>億</t>
         </is>
       </c>
-      <c r="O12" s="199" t="n"/>
+      <c r="O12" s="208" t="n"/>
       <c r="P12" s="164" t="inlineStr">
         <is>
           <t>億</t>

--- a/templates/execution_table_template.xlsx
+++ b/templates/execution_table_template.xlsx
@@ -1723,11 +1723,7 @@
           <t>億</t>
         </is>
       </c>
-      <c r="Q5" s="158" t="inlineStr">
-        <is>
-          <t>売上・経常利益：各決算短信の累計実績（億円）</t>
-        </is>
-      </c>
+      <c r="Q5" s="158" t="n"/>
       <c r="R5" s="57" t="n"/>
       <c r="S5" s="57" t="n"/>
     </row>
@@ -1780,11 +1776,7 @@
           <t>億</t>
         </is>
       </c>
-      <c r="Q6" s="165" t="inlineStr">
-        <is>
-          <t>株価：各四半期末の終値（円、休場日は直前営業日）</t>
-        </is>
-      </c>
+      <c r="Q6" s="165" t="n"/>
       <c r="R6" s="57" t="n"/>
       <c r="S6" s="57" t="n"/>
     </row>
@@ -1837,11 +1829,7 @@
           <t>億</t>
         </is>
       </c>
-      <c r="Q7" s="164" t="inlineStr">
-        <is>
-          <t>予想年度は会社の通期予想のみ、四半期は未発表</t>
-        </is>
-      </c>
+      <c r="Q7" s="164" t="n"/>
       <c r="R7" s="57" t="n"/>
       <c r="S7" s="57" t="n"/>
     </row>
@@ -1894,11 +1882,7 @@
           <t>億</t>
         </is>
       </c>
-      <c r="Q8" s="173" t="inlineStr">
-        <is>
-          <t>業績出典：J-Quants /fins/summary</t>
-        </is>
-      </c>
+      <c r="Q8" s="173" t="n"/>
       <c r="R8" s="57" t="n"/>
       <c r="S8" s="57" t="n"/>
     </row>
@@ -1955,11 +1939,7 @@
           <t>億</t>
         </is>
       </c>
-      <c r="Q9" s="165" t="inlineStr">
-        <is>
-          <t>株価出典：J-Quants /equities/bars/daily</t>
-        </is>
-      </c>
+      <c r="Q9" s="165" t="n"/>
       <c r="R9" s="57" t="n"/>
       <c r="S9" s="57" t="n"/>
     </row>

--- a/templates/execution_table_template.xlsx
+++ b/templates/execution_table_template.xlsx
@@ -1612,7 +1612,11 @@
       <c r="N2" s="55" t="n"/>
       <c r="O2" s="191" t="n"/>
       <c r="P2" s="55" t="n"/>
-      <c r="Q2" s="9" t="n"/>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="R2" s="57" t="n"/>
       <c r="S2" s="57" t="n"/>
     </row>
